--- a/assets/ejemplos excel alimentos/2_aumento_proveedor_alimentos.xlsx
+++ b/assets/ejemplos excel alimentos/2_aumento_proveedor_alimentos.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,31 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +86,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="002563EB"/>
         <bgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,6 +156,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,283 +550,277 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>MOLINOS &amp; BEBIDAS S.A. — LISTA OFICIAL DE PRECIOS SEPTIEMBRE 2026</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Condiciones: Contado contra entrega. Precios sujetos a modificación sin previo aviso.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Cód. Fábrica</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Descripción del Artículo</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Formato Envase</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Nuevo Precio ($)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Estado / Vigencia</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>FAB-01</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Aceite Girasol Cañuelas 1500cc Botella</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Caja x 6</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="12" t="n">
         <v>16200</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>FAB-02</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Harina Trigo Pureza 000 x 1000g</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Fardo x 10</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="15" t="n">
         <v>13900</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>FAB-03</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Arroz Lucchetti Largo Fino 1000 grs</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Fardo x 10</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="12" t="n">
         <v>17800</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>FAB-04</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Fideos Guiseros Matarazzo 500g</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Caja x 15</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="15" t="n">
         <v>20200</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>FAB-05</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Puré de Tomate De Cecco 520 grs Tetra</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Caja x 12</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>FAB-06</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Gaseosa Coca-Cola Sabor Original 2250cc</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Pack x 6</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="15" t="n">
         <v>21500</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>FAB-07</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Cerveza Quilmes Clásica 1000cc Vidrio</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Cajón x 12</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="12" t="n">
         <v>26800</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>FAB-08</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Yerba Mate Playadito x 1 Kilo Tradicional</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Fardo x 10</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="15" t="n">
         <v>42500</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Aumento Vigente</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>FAB-09</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Galletitas Chocolinas Originales 250g</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Caja x 24</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="12" t="n">
         <v>9800</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>LANZAMIENTO NUEVO</t>
         </is>
